--- a/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
+++ b/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="214">
   <si>
     <t xml:space="preserve">Peer-review grading sheet — Chemical Reaction Engineering III, Ulm University</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Date:</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/05/12</t>
+    <t xml:space="preserve">2026/06/03</t>
   </si>
   <si>
     <t xml:space="preserve">Rating scale (used for every criterion below)</t>
@@ -129,13 +129,10 @@
     <t xml:space="preserve">Text quality (language, style, grammar)</t>
   </si>
   <si>
-    <t xml:space="preserve">Clear descriptions, Short, but not too short explanations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slightly little text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maybe a bit more in-depth explanation </t>
+    <t xml:space="preserve">Clear text, nicely readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
   </si>
   <si>
     <t xml:space="preserve">I-2</t>
@@ -144,13 +141,13 @@
     <t xml:space="preserve">Figures (labels, legends, readability, referenced in text)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleary structured figures. Heading, context and legends is choosen nicely. All components can be differenciated easily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instead of „experiment Y“ you could reference a discrete figure.</t>
+    <t xml:space="preserve">Figures look adequately, grid is very helpful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minor mistakes in labeling (e.g. figure 1), better differentiation between lines needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colormap (viridis etc.) can be used for better visualisation, different linestyles would also be suited</t>
   </si>
   <si>
     <t xml:space="preserve">I-3</t>
@@ -159,13 +156,7 @@
     <t xml:space="preserve">Equations (formatting, variables defined, consistent units)</t>
   </si>
   <si>
-    <t xml:space="preserve">good struture, constants and indices look good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tight spacing in between large products (e.g. C_a * c_B), could use \cdot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbering the equations (didn’t do that myself either, because labeling them in independent markdown boxes is a nightmare)</t>
+    <t xml:space="preserve">Everything fine, numbering is present</t>
   </si>
   <si>
     <t xml:space="preserve">I-4</t>
@@ -174,7 +165,7 @@
     <t xml:space="preserve">Report structure (logical flow, balanced sections, headings)</t>
   </si>
   <si>
-    <t xml:space="preserve">Very good structuring, good readability</t>
+    <t xml:space="preserve">Clear structure</t>
   </si>
   <si>
     <t xml:space="preserve">II) Background &amp; Motivation   (category weight: 20%)</t>
@@ -186,10 +177,13 @@
     <t xml:space="preserve">Theoretical background (relevant, accurate, linked to assignment)</t>
   </si>
   <si>
-    <t xml:space="preserve">All balance equations are listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very short overview (thats subjective)</t>
+    <t xml:space="preserve">Theory is very good! Reaction conditions as well as the presence of catalysts in literature work is stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No mathematical approach or explanation is given, its only implemented in code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">definetely give a brief mathematical approach</t>
   </si>
   <si>
     <t xml:space="preserve">II-2</t>
@@ -198,13 +192,13 @@
     <t xml:space="preserve">Motivation &amp; relevance (why the task matters in reaction engineering)</t>
   </si>
   <si>
-    <t xml:space="preserve">Short motivation ist present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A bit short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extend the chapter by typical application</t>
+    <t xml:space="preserve">Straight forward and clear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maybe a bit short, use of DME could have been explained a bit more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a bit more in-detail explanation why we should produce DME</t>
   </si>
   <si>
     <t xml:space="preserve">III-1</t>
@@ -213,7 +207,7 @@
     <t xml:space="preserve">FAIR / readable code (comments, variable names, units, structure)</t>
   </si>
   <si>
-    <t xml:space="preserve">All correct</t>
+    <t xml:space="preserve">Paramters are all described and explained, structuring is really good</t>
   </si>
   <si>
     <t xml:space="preserve">III-2</t>
@@ -222,10 +216,13 @@
     <t xml:space="preserve">Code is supported by report text (methods in code match those described)</t>
   </si>
   <si>
-    <t xml:space="preserve">good explanation in the code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">functions could have been defined closer</t>
+    <t xml:space="preserve">not present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not present in report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add code reference to markdown (e.g. „the function get_thermo_data does…“)</t>
   </si>
   <si>
     <t xml:space="preserve">III-3</t>
@@ -234,7 +231,7 @@
     <t xml:space="preserve">Documentation of applied methods (reproducible: versions, data, seeds)</t>
   </si>
   <si>
-    <t xml:space="preserve">All used tools are displayed</t>
+    <t xml:space="preserve">short comments on the solver functions etc. would be sufficient in my opinion</t>
   </si>
   <si>
     <t xml:space="preserve">III-4</t>
@@ -243,10 +240,13 @@
     <t xml:space="preserve">Validation strategy (analytical limits, literature, convergence, sanity checks)</t>
   </si>
   <si>
-    <t xml:space="preserve">Validation of reaction network is done very precisely. Concentration profiles are compared to the measured data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No explanation of the values of k, no other parameters (e.g. reaction rate exponents) are varied. Values and boundaries of k are not explained</t>
+    <t xml:space="preserve">directly validated calculated data to literature (e.g. reaction data and yield at given conditions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no check for numerical staibility, temperature and pressure range only investigated for literature conditions (→ numerical issues could have happened when investigating broader range)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check convergence, plausibility of initial guesses </t>
   </si>
   <si>
     <t xml:space="preserve">IV) Scientific discussion   (category weight: 35%)</t>
@@ -258,7 +258,29 @@
     <t xml:space="preserve">Plausibility check of results (orders of magnitude, limiting cases)</t>
   </si>
   <si>
-    <t xml:space="preserve">pretty similar to III-4</t>
+    <t xml:space="preserve">Data is generally compared to literature</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">reliability of numerical solution is not discussed, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> parameters are varied over a pre-choosen temperature and pressure range, therefore the model is not tested for suboptimal conditions (high temperatures and low pressures)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">add parts for analyzing the numerical solution, describe the solution approach</t>
   </si>
   <si>
     <t xml:space="preserve">IV-2</t>
@@ -267,10 +289,13 @@
     <t xml:space="preserve">Connection to theory (results discussed against background)</t>
   </si>
   <si>
-    <t xml:space="preserve">Profiles and reaction network is analized well. Kinetics assumed are validated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other parameters are missing, setting different initial values is missing</t>
+    <t xml:space="preserve">Discussion regarding p- and T-dependence is close to general expactations in theory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sometimes a bit short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">further elaborate on general trends </t>
   </si>
   <si>
     <t xml:space="preserve">IV-3</t>
@@ -279,13 +304,13 @@
     <t xml:space="preserve">Significance of the parameter study (informative variation, conclusions drawn)</t>
   </si>
   <si>
-    <t xml:space="preserve">estimated parameters are discussed well. Its consequences (concentration profiles) are also discussed and classified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other parameters (such as different reaction orders) could have been estimated as well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">definen new functions that include reaction orders and compare the results</t>
+    <t xml:space="preserve">Looked into T- and p-ranges stated in literature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small T- and p-range which gives little insight in general reaction system themodynamics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">initially use a broader range of paramters and only limit it after first investigations</t>
   </si>
   <si>
     <t xml:space="preserve">IV-4</t>
@@ -294,13 +319,13 @@
     <t xml:space="preserve">Independent interpretation (own reasoning visible, not template-like)</t>
   </si>
   <si>
-    <t xml:space="preserve">well presented plots, reaction network is worked through again</t>
-  </si>
-  <si>
-    <t xml:space="preserve">closer interpretation would have been nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparison to literature values of different reaction types (to compare the obtained magnitude of parameters), statistics is definetily missing</t>
+    <t xml:space="preserve">Interpretation in general is fine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation is only focussed on the predefined parameters that are varied over a small temperature range, so it only shows that data in the optimal temperature and pressure range is valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use a more general approach for the parameter variation</t>
   </si>
   <si>
     <t xml:space="preserve">IV-5</t>
@@ -309,9 +334,6 @@
     <t xml:space="preserve">Link to industrial application (concrete, realistic scenario)</t>
   </si>
   <si>
-    <t xml:space="preserve">missing</t>
-  </si>
-  <si>
     <t xml:space="preserve">V) Critical &amp; transparent AI use   (category weight: 10%)</t>
   </si>
   <si>
@@ -321,18 +343,12 @@
     <t xml:space="preserve">AI transparency (tools, purposes and example prompts clearly documented)</t>
   </si>
   <si>
-    <t xml:space="preserve">All prompts and AI answers are documented</t>
-  </si>
-  <si>
     <t xml:space="preserve">V-2</t>
   </si>
   <si>
     <t xml:space="preserve">Critical AI evaluation (output verified, errors/hallucinations identified, own understanding visible)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hard to grade, since AI output hasn’t really been used exept for markdown formatting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Result</t>
   </si>
   <si>
@@ -357,7 +373,7 @@
     <t xml:space="preserve">What the authors should keep doing in future assignments.</t>
   </si>
   <si>
-    <t xml:space="preserve">Very good structure and explanation of the code and tools, precise explanation of the assumptions, the whole report is strucured nicely. The plots and figures are very well organized</t>
+    <t xml:space="preserve">Structure of the report is very good, Introduction arouses my interest, thermodynamic data validation is pretty good</t>
   </si>
   <si>
     <t xml:space="preserve">Top 3 things to improve</t>
@@ -366,7 +382,7 @@
     <t xml:space="preserve">Concrete, actionable suggestions — refer to the criteria above.</t>
   </si>
   <si>
-    <t xml:space="preserve">more in-depth validation, statistical evaluation, discussion of viability of the proposed paramters (in this case it works out but in a more coupled system with dependent parameters the solution could be numerically correct but kinetically wrong)</t>
+    <t xml:space="preserve">basic explanation of the code, declaration and reflection on AI usage, broader parametric study (beyond the optimal literature values)</t>
   </si>
   <si>
     <t xml:space="preserve">One question this report raised for you as a reviewer</t>
@@ -375,7 +391,7 @@
     <t xml:space="preserve">What did reviewing this report make you reflect on for your own work?</t>
   </si>
   <si>
-    <t xml:space="preserve">Why did you choose the proposed kinetic terms? Because it was easy to implement or it was the easiest assumption (which would be good!)</t>
+    <t xml:space="preserve">How is the calculation of equilibrium data (yield, reaction extent, etc.) done? (Obviously I know because I did it myself, but from an outside perspective this is unclear</t>
   </si>
   <si>
     <t xml:space="preserve">Reminder: Do NOT use AI tools to generate this peer review. Reflecting on someone else's report is the central learning goal of this exercise.</t>
@@ -894,7 +910,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -985,6 +1001,10 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1540,15 +1560,15 @@
         <v>36</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>39</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>0.1</v>
@@ -1557,24 +1577,24 @@
         <v>0.25</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="H20" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>44</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>0.1</v>
@@ -1586,21 +1606,21 @@
         <v>4</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>0.1</v>
@@ -1612,16 +1632,18 @@
         <v>4</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="19"/>
+        <v>36</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -1633,10 +1655,10 @@
     </row>
     <row r="24" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="17" t="n">
         <v>0.2</v>
@@ -1648,19 +1670,21 @@
         <v>3</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="19"/>
+        <v>52</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="22" t="n">
         <v>0.2</v>
@@ -1672,13 +1696,13 @@
         <v>3</v>
       </c>
       <c r="F25" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1693,10 +1717,10 @@
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="17" t="n">
         <v>0.25</v>
@@ -1708,17 +1732,21 @@
         <v>4</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
+        <v>61</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C28" s="22" t="n">
         <v>0.25</v>
@@ -1727,22 +1755,24 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>0.25</v>
@@ -1751,20 +1781,24 @@
         <v>0.25</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+        <v>64</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0.25</v>
@@ -1773,15 +1807,17 @@
         <v>0.25</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="H30" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
@@ -1814,15 +1850,19 @@
       <c r="F32" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="G32" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="22" t="n">
         <v>0.35</v>
@@ -1834,19 +1874,21 @@
         <v>3</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="19"/>
+        <v>84</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C34" s="17" t="n">
         <v>0.35</v>
@@ -1858,21 +1900,21 @@
         <v>2</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C35" s="22" t="n">
         <v>0.35</v>
@@ -1881,24 +1923,24 @@
         <v>0.2</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C36" s="17" t="n">
         <v>0.35</v>
@@ -1911,28 +1953,28 @@
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="19" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="H36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
+      <c r="A37" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>0.1</v>
@@ -1941,20 +1983,20 @@
         <v>0.5</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>0.1</v>
@@ -1963,10 +2005,10 @@
         <v>0.5</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
@@ -1990,9 +2032,9 @@
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="25" t="n">
         <f aca="false">((0.025*E19) + (0.025*E20) + (0.025*E21) + (0.025*E22) + (0.1*E24) + (0.1*E25) + (0.0625*E27) + (0.0625*E28) + (0.0625*E29) + (0.0625*E30) + (0.07*E32) + (0.07*E33) + (0.07*E34) + (0.07*E35) + (0.07*E36) + (0.05*E38) + (0.05*E39))/4</f>
-        <v>0.698125</v>
+        <v>0.521875</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>105</v>
@@ -2007,9 +2049,9 @@
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="25" t="n">
+      <c r="E43" s="26" t="n">
         <f aca="false">E42*100</f>
-        <v>69.8125</v>
+        <v>52.1875</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>107</v>
@@ -2030,124 +2072,124 @@
       <c r="H45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
     </row>
     <row r="48" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
     </row>
     <row r="52" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
     </row>
     <row r="56" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2254,169 +2296,169 @@
       <c r="A3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="32" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="32" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="32" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="32" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="32" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="32" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="32" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="32" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="32" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2424,118 +2466,118 @@
       <c r="A13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="32" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="32" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="32" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="32" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="32" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="32" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="32" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2572,10 +2614,10 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
@@ -2584,13 +2626,13 @@
       <c r="B3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="34"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -2598,7 +2640,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B6" s="16" t="s">
@@ -2606,7 +2648,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -2614,7 +2656,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B8" s="16" t="s">
@@ -2622,7 +2664,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B9" s="16" t="s">
@@ -2630,13 +2672,13 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -2644,7 +2686,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B12" s="16" t="s">
@@ -2652,7 +2694,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -2660,10 +2702,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="33"/>
+      <c r="B14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
@@ -2672,13 +2714,13 @@
       <c r="B15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="B16" s="33"/>
+      <c r="B16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B17" s="16" t="s">
@@ -2686,7 +2728,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B18" s="16" t="s">
@@ -2694,7 +2736,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B19" s="16" t="s">
@@ -2702,7 +2744,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B20" s="16" t="s">
@@ -2710,7 +2752,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B21" s="16" t="s">
@@ -2718,7 +2760,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="35" t="s">
         <v>195</v>
       </c>
       <c r="B22" s="16" t="s">

--- a/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
+++ b/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="217">
   <si>
     <t xml:space="preserve">Peer-review grading sheet — Chemical Reaction Engineering III, Ulm University</t>
   </si>
@@ -343,10 +343,19 @@
     <t xml:space="preserve">AI transparency (tools, purposes and example prompts clearly documented)</t>
   </si>
   <si>
+    <t xml:space="preserve">Not present in report, only given in additional document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use chat links and adapt them into the markdown, write an additional chapter for AI usage, I almost didnt find the prompt documentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">V-2</t>
   </si>
   <si>
     <t xml:space="preserve">Critical AI evaluation (output verified, errors/hallucinations identified, own understanding visible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">please explain the AI usage and reflect on it</t>
   </si>
   <si>
     <t xml:space="preserve">Result</t>
@@ -1983,20 +1992,22 @@
         <v>0.5</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="19"/>
+      <c r="G38" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>0.1</v>
@@ -2011,11 +2022,13 @@
         <v>64</v>
       </c>
       <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
+      <c r="H39" s="19" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2027,41 +2040,41 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="25" t="n">
         <f aca="false">((0.025*E19) + (0.025*E20) + (0.025*E21) + (0.025*E22) + (0.1*E24) + (0.1*E25) + (0.0625*E27) + (0.0625*E28) + (0.0625*E29) + (0.0625*E30) + (0.07*E32) + (0.07*E33) + (0.07*E34) + (0.07*E35) + (0.07*E36) + (0.05*E38) + (0.05*E39))/4</f>
-        <v>0.521875</v>
+        <v>0.534375</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="26" t="n">
         <f aca="false">E42*100</f>
-        <v>52.1875</v>
+        <v>53.4375</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -2073,7 +2086,7 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B46" s="27"/>
       <c r="C46" s="27"/>
@@ -2085,7 +2098,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B47" s="28"/>
       <c r="C47" s="28"/>
@@ -2097,7 +2110,7 @@
     </row>
     <row r="48" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
@@ -2109,7 +2122,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B50" s="27"/>
       <c r="C50" s="27"/>
@@ -2121,7 +2134,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B51" s="28"/>
       <c r="C51" s="28"/>
@@ -2133,7 +2146,7 @@
     </row>
     <row r="52" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -2145,7 +2158,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B54" s="27"/>
       <c r="C54" s="27"/>
@@ -2157,7 +2170,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
@@ -2169,7 +2182,7 @@
     </row>
     <row r="56" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="29" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
@@ -2181,7 +2194,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
@@ -2268,7 +2281,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2283,13 +2296,13 @@
         <v>25</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2297,16 +2310,16 @@
         <v>33</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2314,16 +2327,16 @@
         <v>37</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2331,16 +2344,16 @@
         <v>42</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2348,16 +2361,16 @@
         <v>45</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2365,16 +2378,16 @@
         <v>49</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2382,16 +2395,16 @@
         <v>54</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2399,16 +2412,16 @@
         <v>59</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2416,16 +2429,16 @@
         <v>62</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2433,16 +2446,16 @@
         <v>67</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2450,16 +2463,16 @@
         <v>70</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2467,16 +2480,16 @@
         <v>76</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2484,16 +2497,16 @@
         <v>81</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2501,16 +2514,16 @@
         <v>86</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2518,16 +2531,16 @@
         <v>91</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2535,16 +2548,16 @@
         <v>96</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2552,33 +2565,33 @@
         <v>99</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2609,162 +2622,162 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B2" s="34"/>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B4" s="34"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="34" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="34" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
+++ b/Peer Review Group 3/Grading Group 3 Julian Stierstorfer.xlsx
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
